--- a/State_Contacts.xlsx
+++ b/State_Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8bdff5c664b19dc0/2025/Strategic_Accounts_App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{AB8E7485-E921-4A2D-B423-CAC103FA3C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F0DD499-5F7B-4DFF-BA1C-BE452B6CA7FD}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{AB8E7485-E921-4A2D-B423-CAC103FA3C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4054FC50-155B-4922-80BB-0D5713ED8F51}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="12" r:id="rId1"/>
@@ -6203,6 +6203,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -6496,7 +6500,8 @@
   <dimension ref="A1:W149"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="14" width="17.85546875" style="268" customWidth="1"/>
+    <col min="1" max="1" width="40.85546875" style="268" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="17.85546875" style="268" customWidth="1"/>
     <col min="15" max="15" width="47.85546875" style="268" customWidth="1"/>
     <col min="16" max="16" width="22" style="268" customWidth="1"/>
     <col min="17" max="17" width="23.140625" style="268" customWidth="1"/>
@@ -31231,6 +31236,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="83fa0e72-4838-4c87-ade5-9d74fac4b7f1">
@@ -31334,15 +31348,6 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23B95257-FB04-42B1-8130-30C4003BE261}">
   <ds:schemaRefs>
@@ -31363,6 +31368,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68753433-8772-4A02-9846-3D24210F80DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2B42006-1D58-4F9E-91DE-E6850682C173}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="83fa0e72-4838-4c87-ade5-9d74fac4b7f1"/>
@@ -31379,14 +31392,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68753433-8772-4A02-9846-3D24210F80DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{fba19210-32fa-4fbc-bd55-f9e1dc3bf117}" enabled="0" method="" siteId="{fba19210-32fa-4fbc-bd55-f9e1dc3bf117}" removed="1"/>
